--- a/data/trans_bre/IP04F-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP04F-Estudios-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 11,36</t>
+          <t>-3,21; 10,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 5,86</t>
+          <t>-7,23; 5,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-44,76; 397,49</t>
+          <t>-45,64; 402,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-84,76; 386,32</t>
+          <t>-86,57; 326,16</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 3,5</t>
+          <t>-1,59; 3,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 3,48</t>
+          <t>-1,64; 3,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-23,07; 76,34</t>
+          <t>-23,24; 79,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-23,66; 93,76</t>
+          <t>-25,03; 81,47</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 8,12</t>
+          <t>-6,79; 7,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 9,06</t>
+          <t>-3,66; 9,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-26,06; 50,32</t>
+          <t>-28,81; 46,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,06; 72,86</t>
+          <t>-19,67; 75,17</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 3,73</t>
+          <t>-1,01; 3,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,64</t>
+          <t>-1,23; 3,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 46,41</t>
+          <t>-10,38; 51,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,68; 54,23</t>
+          <t>-15,12; 51,07</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04F-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP04F-Estudios-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 10,76</t>
+          <t>-3,28; 10,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 5,61</t>
+          <t>-6,76; 5,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-45,64; 402,38</t>
+          <t>-39,79; 364,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-86,57; 326,16</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 3,58</t>
+          <t>-1,58; 3,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 3,27</t>
+          <t>-1,56; 3,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-23,24; 79,07</t>
+          <t>-22,51; 76,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-25,03; 81,47</t>
+          <t>-25,0; 86,62</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 7,33</t>
+          <t>-6,76; 8,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 9,35</t>
+          <t>-3,66; 9,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-28,81; 46,75</t>
+          <t>-29,0; 51,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 75,17</t>
+          <t>-20,69; 72,77</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 3,92</t>
+          <t>-1,17; 3,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 3,48</t>
+          <t>-1,13; 3,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 51,36</t>
+          <t>-11,05; 53,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,12; 51,07</t>
+          <t>-13,71; 50,74</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04F-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP04F-Estudios-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 10,68</t>
+          <t>-2,94; 11,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 5,4</t>
+          <t>-6,65; 5,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-39,79; 364,39</t>
+          <t>-44,76; 397,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-84,76; 386,32</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 3,5</t>
+          <t>-1,55; 3,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,45</t>
+          <t>-1,45; 3,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,51; 76,95</t>
+          <t>-23,07; 76,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-25,0; 86,62</t>
+          <t>-23,66; 93,76</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 8,47</t>
+          <t>-6,18; 8,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 9,57</t>
+          <t>-3,53; 9,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-29,0; 51,38</t>
+          <t>-26,06; 50,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,69; 72,77</t>
+          <t>-19,06; 72,86</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 3,96</t>
+          <t>-1,02; 3,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 3,37</t>
+          <t>-1,27; 3,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 53,47</t>
+          <t>-10,44; 46,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 50,74</t>
+          <t>-14,68; 54,23</t>
         </is>
       </c>
     </row>
